--- a/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 15,06</t>
+          <t>-13,25; 15,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 15,72</t>
+          <t>-23,29; 12,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 40,25</t>
+          <t>-26,49; 35,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 36,35</t>
+          <t>-23,14; 38,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 36,28</t>
+          <t>-37,97; 28,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,48; 161,2</t>
+          <t>-58,2; 118,52</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -2,89</t>
+          <t>-15,52; -2,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -2,56</t>
+          <t>-16,01; -3,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,41; -11,57</t>
+          <t>-33,76; -11,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,69; -5,8</t>
+          <t>-27,25; -5,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,39; -6,33</t>
+          <t>-33,7; -8,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,57; -27,92</t>
+          <t>-66,43; -26,9</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 0,28</t>
+          <t>-21,11; 0,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,8; -5,07</t>
+          <t>-25,31; -5,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 12,12</t>
+          <t>-13,96; 12,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 1,16</t>
+          <t>-37,17; 0,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,14; -12,81</t>
+          <t>-51,76; -13,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 59,0</t>
+          <t>-38,83; 58,2</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,93; -3,57</t>
+          <t>-13,97; -3,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -5,62</t>
+          <t>-15,46; -5,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,69; -5,26</t>
+          <t>-23,91; -5,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,6; -7,04</t>
+          <t>-24,98; -6,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,25; -13,07</t>
+          <t>-32,46; -13,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -14,83</t>
+          <t>-56,15; -15,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 15,2</t>
+          <t>-14,98; 15,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 12,88</t>
+          <t>-21,45; 13,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 35,28</t>
+          <t>-21,57; 38,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 38,25</t>
+          <t>-24,96; 34,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 28,06</t>
+          <t>-35,9; 31,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 118,52</t>
+          <t>-48,85; 136,63</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,52; -2,97</t>
+          <t>-16,09; -3,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -3,64</t>
+          <t>-15,48; -3,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,76; -11,47</t>
+          <t>-34,0; -11,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,25; -5,88</t>
+          <t>-27,96; -6,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,7; -8,5</t>
+          <t>-32,44; -8,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,43; -26,9</t>
+          <t>-70,1; -28,07</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 0,13</t>
+          <t>-21,73; 0,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,31; -5,29</t>
+          <t>-25,7; -4,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 12,69</t>
+          <t>-14,12; 12,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 0,27</t>
+          <t>-37,23; 0,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,76; -13,62</t>
+          <t>-50,93; -11,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 58,2</t>
+          <t>-39,74; 56,97</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,97; -3,62</t>
+          <t>-13,36; -3,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,62</t>
+          <t>-15,46; -5,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,91; -5,89</t>
+          <t>-22,98; -5,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,98; -6,97</t>
+          <t>-23,82; -6,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -13,35</t>
+          <t>-32,44; -12,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,15; -15,81</t>
+          <t>-52,49; -13,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>-14,09</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>-32,89%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 15,31</t>
+          <t>-13,55; 15,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 13,97</t>
+          <t>-19,81; 15,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 38,29</t>
+          <t>-37,56; 13,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,96; 34,78</t>
+          <t>-23,85; 36,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 31,23</t>
+          <t>-32,73; 36,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,85; 136,63</t>
+          <t>-74,61; 50,53</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-20,6</t>
+          <t>-17,56</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-45,28%</t>
+          <t>-38,94%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -3,62</t>
+          <t>-15,77; -2,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -3,65</t>
+          <t>-14,84; -2,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,0; -11,86</t>
+          <t>-26,27; -8,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,96; -6,82</t>
+          <t>-27,69; -5,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -8,48</t>
+          <t>-31,39; -6,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,1; -28,07</t>
+          <t>-53,25; -21,3</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,43%</t>
+          <t>-3,0%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 0,24</t>
+          <t>-21,33; 0,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,7; -4,41</t>
+          <t>-25,8; -5,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 12,75</t>
+          <t>-15,72; 12,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 0,64</t>
+          <t>-36,46; 1,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,93; -11,04</t>
+          <t>-51,14; -12,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 56,97</t>
+          <t>-41,27; 56,86</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-13,7</t>
+          <t>-13,27</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-33,37%</t>
+          <t>-32,29%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -3,33</t>
+          <t>-13,93; -3,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,46; -5,53</t>
+          <t>-15,38; -5,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,98; -5,23</t>
+          <t>-20,15; -5,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,82; -6,34</t>
+          <t>-24,6; -7,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,44; -12,72</t>
+          <t>-32,25; -13,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,49; -13,56</t>
+          <t>-44,69; -15,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,91</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-14,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,37%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-32,89%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.5124859681444827</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.90536646600439</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-14.08550525916944</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.01013291435132873</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.07373507400261498</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3288599066643763</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,55; 15,06</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-19,81; 15,72</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-37,56; 13,49</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-23,85; 36,35</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-32,73; 36,28</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-74,61; 50,53</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-13.54639145829836</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-19.80682552222425</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-37.56460941483397</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.2384595919079368</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3272913385895114</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.746062025350715</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15.06441006236638</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.72041515257811</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.49153085485668</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.3634916358755692</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3627813529073654</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.5053331973017869</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-9,8</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-9,49</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-17,56</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-17,97%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-21,4%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-38,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-15,77; -2,89</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-14,84; -2,56</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-26,27; -8,7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-27,69; -5,8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-31,39; -6,33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-53,25; -21,3</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-9.804997591569336</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-9.491714470840995</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-17.55552656656306</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1796524706503638</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2140289485570073</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3893744593664384</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-10,49</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-15,6</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-19,83%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-34,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-3,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-15.77125653608882</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-14.83621957684899</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-26.26700841779577</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.2769209026523767</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3139435840941678</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5325095215512656</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-21,33; 0,28</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-25,8; -5,07</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-15,72; 12,18</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-36,46; 1,16</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-51,14; -12,81</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-41,27; 56,86</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-2.889060293007475</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-2.564695425198301</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-8.704779898855286</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.05798961714798011</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.06325703927947109</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.212996142139068</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +767,161 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-8,71</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-10,57</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-13,27</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-16,21%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-23,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-32,29%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-10.48766086982852</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-15.59583773493697</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.8736129022005823</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.1983384920727752</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3445258748631761</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.0300016552128255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-13,93; -3,57</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-15,38; -5,62</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-20,15; -5,98</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-24,6; -7,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-32,25; -13,07</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-44,69; -15,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-21.32724187344511</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-25.797715340228</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-15.7222871699862</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.3645815728360277</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5113529177186147</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4127001187506958</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2753980864671604</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-5.067551230589834</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>12.17874188608922</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.01163584551624161</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.1280596412721086</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.5686033539101565</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-8.711885618280462</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-10.57482590979102</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-13.26536667653281</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.1620684880322154</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2331172834798522</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3228542747710854</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-13.9275006114151</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-15.3838240810823</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-20.14601592282918</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.2459735565544291</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3225077584074911</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.446906198301255</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-3.572484058533521</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-5.620049701465927</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-5.984524863334173</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.07044606513105635</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.1306902523445392</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.1588974907982745</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +930,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R2-Estudios-trans_bre.xlsx
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5124859681444827</v>
+        <v>2.146691217830305</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-3.90536646600439</v>
+        <v>-2.21094468266731</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-14.08550525916944</v>
+        <v>-8.890340771067146</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.01013291435132873</v>
+        <v>0.04609553716021909</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.07373507400261498</v>
+        <v>-0.04670656650169446</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>-0.3288599066643763</v>
+        <v>-0.2075663302375591</v>
       </c>
     </row>
     <row r="5">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-13.54639145829836</v>
+        <v>-11.23806757744062</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-19.80682552222425</v>
+        <v>-18.60932090612626</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-37.56460941483397</v>
+        <v>-34.62613197030561</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.2384595919079368</v>
+        <v>-0.2146241768839635</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.3272913385895114</v>
+        <v>-0.3389630569612561</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-0.746062025350715</v>
+        <v>-0.632707599391452</v>
       </c>
     </row>
     <row r="6">
@@ -656,22 +656,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>15.06441006236638</v>
+        <v>16.27168273402865</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>15.72041515257811</v>
+        <v>12.30262563485934</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>13.49153085485668</v>
+        <v>15.56862877016132</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.3634916358755692</v>
+        <v>0.4197487341438308</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.3627813529073654</v>
+        <v>0.3302604139656898</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5053331973017869</v>
+        <v>0.5212294496413878</v>
       </c>
     </row>
     <row r="7">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-9.804997591569336</v>
+        <v>-8.067422137309787</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-9.491714470840995</v>
+        <v>-11.39465941089981</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-17.55552656656306</v>
+        <v>-17.06135111459454</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1796524706503638</v>
+        <v>-0.1525534031011085</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.2140289485570073</v>
+        <v>-0.2554160604809799</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.3893744593664384</v>
+        <v>-0.3786919675505996</v>
       </c>
     </row>
     <row r="8">
@@ -712,22 +712,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-15.77125653608882</v>
+        <v>-13.87105589905067</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-14.83621957684899</v>
+        <v>-16.83932832333943</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-26.26700841779577</v>
+        <v>-24.91587018256535</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.2769209026523767</v>
+        <v>-0.247075724902084</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.3139435840941678</v>
+        <v>-0.3567036363697921</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.5325095215512656</v>
+        <v>-0.5065131277029485</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-2.889060293007475</v>
+        <v>-1.70996682072029</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-2.564695425198301</v>
+        <v>-5.480523704404739</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>-8.704779898855286</v>
+        <v>-7.527963356629051</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>-0.05798961714798011</v>
+        <v>-0.03170996229582893</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.06325703927947109</v>
+        <v>-0.1317074803919807</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.212996142139068</v>
+        <v>-0.1756927442720536</v>
       </c>
     </row>
     <row r="10">
@@ -768,22 +768,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-10.48766086982852</v>
+        <v>-9.794919157002457</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-15.59583773493697</v>
+        <v>-12.51798114913484</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.8736129022005823</v>
+        <v>-0.7832824731348553</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.1983384920727752</v>
+        <v>-0.1871981961608885</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.3445258748631761</v>
+        <v>-0.2782624100940428</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.0300016552128255</v>
+        <v>-0.02671691807782093</v>
       </c>
     </row>
     <row r="11">
@@ -794,22 +794,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-21.32724187344511</v>
+        <v>-19.725781132416</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-25.797715340228</v>
+        <v>-21.60487336943329</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-15.7222871699862</v>
+        <v>-14.17961296200028</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.3645815728360277</v>
+        <v>-0.350861046035214</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.5113529177186147</v>
+        <v>-0.4352080642844396</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.4127001187506958</v>
+        <v>-0.3869423012756072</v>
       </c>
     </row>
     <row r="12">
@@ -820,22 +820,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.2753980864671604</v>
+        <v>0.1282854673144241</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-5.067551230589834</v>
+        <v>-3.013280024349676</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>12.17874188608922</v>
+        <v>11.85870293310441</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.01163584551624161</v>
+        <v>0.002842400760342283</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.1280596412721086</v>
+        <v>-0.07038649057398266</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.5686033539101565</v>
+        <v>0.5209039632752097</v>
       </c>
     </row>
     <row r="13">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-8.711885618280462</v>
+        <v>-7.184062047760054</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-10.57482590979102</v>
+        <v>-10.88127001684109</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-13.26536667653281</v>
+        <v>-12.46363156716541</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.1620684880322154</v>
+        <v>-0.1381709817373185</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2331172834798522</v>
+        <v>-0.2419034241351145</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.3228542747710854</v>
+        <v>-0.3034767286308563</v>
       </c>
     </row>
     <row r="14">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-13.9275006114151</v>
+        <v>-11.64606082849673</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-15.3838240810823</v>
+        <v>-15.66595578458453</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-20.14601592282918</v>
+        <v>-19.1255319430711</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.2459735565544291</v>
+        <v>-0.2147579502316978</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.3225077584074911</v>
+        <v>-0.3299600247251513</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.446906198301255</v>
+        <v>-0.4330102884720939</v>
       </c>
     </row>
     <row r="15">
@@ -902,22 +902,22 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>-3.572484058533521</v>
+        <v>-1.95247497077164</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>-5.620049701465927</v>
+        <v>-6.128327594752905</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-5.984524863334173</v>
+        <v>-5.308390083759676</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.07044606513105635</v>
+        <v>-0.04019276466448422</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.1306902523445392</v>
+        <v>-0.1462447275305425</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.1588974907982745</v>
+        <v>-0.142484835388745</v>
       </c>
     </row>
     <row r="16">
